--- a/stable Work/OpenManipulatorTrajectoryProject_Stable/code/trajectory_full.xlsx
+++ b/stable Work/OpenManipulatorTrajectoryProject_Stable/code/trajectory_full.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Calibration" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full_Trajectory'!$A$1:$M$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full_Trajectory'!$A$1:$M$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calibration'!$A$1:$B$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,22 +432,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M103"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,40 +522,40 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>168.6621115765461</v>
+        <v>168.5742198507731</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>179.5605435726808</v>
+        <v>179.0331932180424</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>355.6054654476808</v>
+        <v>355.6933571734539</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>82.88086607997217</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.003067999999999782</v>
+        <v>0.001533999999999891</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>-0.004602000000000169</v>
+        <v>-0.01380600000000001</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0.004602000000000169</v>
+        <v>-0.003067999999999782</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.446544</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>181.4527144862103</v>
+        <v>181.5198201061434</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.5566986747098516</v>
+        <v>0.2784516224562071</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>41.52379073831096</v>
+        <v>42.85876837182275</v>
       </c>
     </row>
     <row r="3">
@@ -566,37 +566,37 @@
         <v>0.051</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>168.7500033023192</v>
+        <v>168.9257867538653</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>180.7031360077307</v>
+        <v>179.2968683953616</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>356.3964909796384</v>
+        <v>355.869140625</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>82.88086607997217</v>
+        <v>82.96875780574523</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.004602000000000169</v>
+        <v>0.007669999999999951</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.0153399999999999</v>
+        <v>-0.009203999999999843</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.009204000000000339</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.446544</v>
+        <v>1.448078</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>178.4156901829581</v>
+        <v>180.606502611762</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.8210748025814819</v>
+        <v>1.385279039952783</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>36.19663594613547</v>
+        <v>41.59654120080927</v>
       </c>
     </row>
     <row r="4">
@@ -607,37 +607,37 @@
         <v>0.101</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>168.8378950280923</v>
+        <v>169.3652453827307</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>182.3730215016395</v>
+        <v>179.7363270242269</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>357.2754082373691</v>
+        <v>356.0449240765461</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>82.70508262842601</v>
+        <v>83.05664953151829</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.00613600000000006</v>
+        <v>0.0153399999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.04448500000000007</v>
+        <v>-0.001533999999999891</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.02454400000000024</v>
+        <v>0.003067999999999782</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.443476</v>
+        <v>1.449612</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>175.0232551424835</v>
+        <v>179.5611324639537</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1.073956171915638</v>
+        <v>2.754683848747697</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>29.33471708724878</v>
+        <v>39.83113232763912</v>
       </c>
     </row>
     <row r="5">
@@ -648,37 +648,37 @@
         <v>0.151</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>169.0136784796384</v>
+        <v>169.6289205600499</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>183.5156139366894</v>
+        <v>179.82421875</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>357.8906503177806</v>
+        <v>356.1328158023192</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>82.61719090265295</v>
+        <v>83.23243298306443</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.009203999999999843</v>
+        <v>0.01994200000000007</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.06442700000000014</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.03528199999999997</v>
+        <v>0.004602000000000169</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.441942</v>
+        <v>1.45268</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>172.3966674502202</v>
+        <v>178.7320970296438</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1.586783734860851</v>
+        <v>3.564748038491168</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>24.71619225363204</v>
+        <v>39.29577203791121</v>
       </c>
     </row>
     <row r="6">
@@ -689,37 +689,37 @@
         <v>0.201</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>169.0136784796384</v>
+        <v>169.804704011596</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>184.1308560171008</v>
+        <v>179.82421875</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>358.1543254950998</v>
+        <v>356.1328158023192</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>82.61719090265295</v>
+        <v>83.58399988615669</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.009203999999999843</v>
+        <v>0.02300999999999985</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.07516499999999987</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.03988400000000014</v>
+        <v>0.004602000000000169</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.441942</v>
+        <v>1.458816</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>171.0047800372038</v>
+        <v>177.710048090496</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1.573972441345739</v>
+        <v>4.089830032647237</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>22.41748732338061</v>
+        <v>39.18370570872921</v>
       </c>
     </row>
     <row r="7">
@@ -730,37 +730,37 @@
         <v>0.251</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>169.0136784796384</v>
+        <v>169.804704011596</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>184.39453119442</v>
+        <v>179.9121104757731</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>358.2421599250933</v>
+        <v>356.1328158023192</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>82.61719090265295</v>
+        <v>84.02345851502204</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.009203999999999843</v>
+        <v>0.02300999999999985</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.07976700000000003</v>
+        <v>0.001533999999999891</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.04141700000000029</v>
+        <v>0.004602000000000169</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.441942</v>
+        <v>1.466486</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>170.4773875683208</v>
+        <v>176.3886506788939</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1.569118183987467</v>
+        <v>4.059419310928897</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>21.49543073920364</v>
+        <v>38.80005777220663</v>
       </c>
     </row>
     <row r="8">
@@ -771,37 +771,37 @@
         <v>0.301</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>169.1015702054115</v>
+        <v>170.1562709146883</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>184.306639468647</v>
+        <v>179.82421875</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>358.2421599250933</v>
+        <v>356.0449240765461</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>82.61719090265295</v>
+        <v>84.28713369234124</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.01073800000000023</v>
+        <v>0.02914599999999991</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.07823300000000015</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.04141700000000029</v>
+        <v>0.003067999999999782</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.441942</v>
+        <v>1.471088</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>170.5589656150213</v>
+        <v>175.9130599698796</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1.831532568052178</v>
+        <v>5.128614362501532</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>21.73861075075655</v>
+        <v>39.19273195501881</v>
       </c>
     </row>
     <row r="9">
@@ -812,37 +812,37 @@
         <v>0.351</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>169.5410288342768</v>
+        <v>171.0351308766395</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>184.1308560171008</v>
+        <v>179.82421875</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>358.2421599250933</v>
+        <v>356.0449240765461</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>82.70508262842601</v>
+        <v>84.28713369234124</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.01840800000000018</v>
+        <v>0.04448500000000007</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.07516499999999987</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.04141700000000029</v>
+        <v>0.003067999999999782</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.443476</v>
+        <v>1.471088</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>170.4530102013468</v>
+        <v>175.813700799582</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>3.138053467602351</v>
+        <v>7.826235646897923</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>22.22243238463938</v>
+        <v>39.19273195501881</v>
       </c>
     </row>
     <row r="10">
@@ -853,37 +853,37 @@
         <v>0.401</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>170.3320543662344</v>
+        <v>172.0019398601432</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>183.8671808397816</v>
+        <v>179.82421875</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>358.1543254950998</v>
+        <v>356.0449240765461</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>82.61719090265295</v>
+        <v>84.28713369234124</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.03221400000000019</v>
+        <v>0.06135899999999986</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.0705630000000002</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.03988400000000014</v>
+        <v>0.003067999999999782</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.441942</v>
+        <v>1.471088</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>171.1703728025461</v>
+        <v>175.6566178775981</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>5.51599057946929</v>
+        <v>10.79166108850693</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>23.14983076224951</v>
+        <v>39.19273195501881</v>
       </c>
     </row>
     <row r="11">
@@ -894,37 +894,37 @@
         <v>0.451</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>171.1230226024125</v>
+        <v>173.05664056942</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>183.6035056624624</v>
+        <v>179.82421875</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>358.2421599250933</v>
+        <v>356.0449240765461</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>82.61719090265295</v>
+        <v>84.37502541811432</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.04601899999999996</v>
+        <v>0.07976700000000003</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.06596100000000003</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.04141700000000029</v>
+        <v>0.003067999999999782</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.441942</v>
+        <v>1.472622</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>171.0475960322414</v>
+        <v>175.1760040618834</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>7.877000608725213</v>
+        <v>14.00297618055902</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>23.688641746039</v>
+        <v>39.16839982647977</v>
       </c>
     </row>
     <row r="12">
@@ -935,37 +935,37 @@
         <v>0.501</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>172.0019398601432</v>
+        <v>173.9355578271507</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>183.1640470335971</v>
+        <v>179.9121104757731</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>358.2421599250933</v>
+        <v>355.9570323507731</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>82.61719090265295</v>
+        <v>84.37502541811432</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.06135899999999986</v>
+        <v>0.09510699999999994</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.05829100000000008</v>
+        <v>0.001533999999999891</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.04141700000000029</v>
+        <v>0.001534000000000387</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.441942</v>
+        <v>1.472622</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>171.306264976218</v>
+        <v>175.1360328594377</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>10.52439228477867</v>
+        <v>16.70706678774907</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>24.9114686436231</v>
+        <v>39.13143323896421</v>
       </c>
     </row>
     <row r="13">
@@ -976,37 +976,37 @@
         <v>0.551</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>172.968748843647</v>
+        <v>174.9902585364275</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>182.8124801305048</v>
+        <v>179.9121104757731</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>358.3300516508664</v>
+        <v>355.9570323507731</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>82.52929917687987</v>
+        <v>84.37502541811432</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.07823300000000015</v>
+        <v>0.1135150000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.05215500000000002</v>
+        <v>0.001533999999999891</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.04295099999999968</v>
+        <v>0.001534000000000387</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.440408</v>
+        <v>1.472622</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>171.399015019874</v>
+        <v>174.7988345670898</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>13.43648255970176</v>
+        <v>19.92795825917761</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>25.70254857313896</v>
+        <v>39.13143323896421</v>
       </c>
     </row>
     <row r="14">
@@ -1017,37 +1017,37 @@
         <v>0.601</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>174.0234495529238</v>
+        <v>176.3964688530171</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>182.3730215016395</v>
+        <v>179.9121104757731</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>358.3300516508664</v>
+        <v>356.1328158023192</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>82.61719090265295</v>
+        <v>84.37502541811432</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.09664099999999984</v>
+        <v>0.1380580000000001</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.04448500000000007</v>
+        <v>0.001533999999999891</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0.04295099999999968</v>
+        <v>0.004602000000000169</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.441942</v>
+        <v>1.472622</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>171.2529912630999</v>
+        <v>173.7540869806019</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>16.6017765400278</v>
+        <v>24.14171746010404</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>26.9199348364202</v>
+        <v>38.70350568316451</v>
       </c>
     </row>
     <row r="15">
@@ -1058,37 +1058,37 @@
         <v>0.651</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>175.2539337137467</v>
+        <v>177.8906281911593</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>181.7578367170075</v>
+        <v>179.9121104757731</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>358.5937268281856</v>
+        <v>356.0449240765461</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>82.52929917687987</v>
+        <v>84.46291714388738</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.1181169999999998</v>
+        <v>0.1641360000000003</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.03374800000000008</v>
+        <v>0.001533999999999891</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.04755299999999985</v>
+        <v>0.003067999999999782</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.440408</v>
+        <v>1.474156</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>170.8275491486227</v>
+        <v>173.0665197315209</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>20.27200121714826</v>
+        <v>28.6643213861165</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>28.04668806789857</v>
+        <v>38.89371892292257</v>
       </c>
     </row>
     <row r="16">
@@ -1099,37 +1099,37 @@
         <v>0.701</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>176.4843605787902</v>
+        <v>179.5605709808476</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>181.2304863623691</v>
+        <v>180.0000022015461</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>359.0331854570509</v>
+        <v>355.9570323507731</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>82.52929917687987</v>
+        <v>84.37502541811432</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.139592</v>
+        <v>0.1932820000000001</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.02454400000000024</v>
+        <v>0.003067999999999782</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.0552229999999998</v>
+        <v>0.001534000000000387</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.440408</v>
+        <v>1.472622</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>169.4596261153197</v>
+        <v>172.5986730905505</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>23.81006312000228</v>
+        <v>33.78194267624404</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>28.5040881233009</v>
+        <v>38.88000697916854</v>
       </c>
     </row>
     <row r="17">
@@ -1140,37 +1140,37 @@
         <v>0.751</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>177.7148447396131</v>
+        <v>181.5820233778486</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>180.7910277335037</v>
+        <v>180.0000022015461</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>359.6484275374624</v>
+        <v>355.9570323507731</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>82.61719090265295</v>
+        <v>84.28713369234124</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.161068</v>
+        <v>0.2285629999999999</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.01687399999999979</v>
+        <v>0.003067999999999782</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.06596099999999953</v>
+        <v>0.001534000000000387</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.441942</v>
+        <v>1.471088</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>167.1618653324432</v>
+        <v>171.5461220928312</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>27.15970168791154</v>
+        <v>39.90644678562288</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>28.29245035853171</v>
+        <v>38.90395095195115</v>
       </c>
     </row>
     <row r="18">
@@ -1181,37 +1181,37 @@
         <v>0.801</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>178.9453289004361</v>
+        <v>183.7793165221753</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>180.1757856530923</v>
+        <v>179.9121104757731</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.3515613436469494</v>
+        <v>355.869140625</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>82.52929917687987</v>
+        <v>84.19924196656818</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.1825439999999999</v>
+        <v>0.2669130000000001</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.00613600000000006</v>
+        <v>0.001533999999999891</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.07823299999999965</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.440408</v>
+        <v>1.469554</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>165.1758450302899</v>
+        <v>170.4338228316012</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>30.49129436530133</v>
+        <v>46.60300070421662</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>28.37640521745055</v>
+        <v>39.39580933969913</v>
       </c>
     </row>
     <row r="19">
@@ -1222,37 +1222,37 @@
         <v>0.851</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>180.3515392170257</v>
+        <v>186.0644440964956</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>179.7363270242269</v>
+        <v>180.0000022015461</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1.054695149831502</v>
+        <v>355.7812488992269</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>82.52929917687987</v>
+        <v>84.02345851502204</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.2070869999999999</v>
+        <v>0.306796</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>-0.001533999999999891</v>
+        <v>0.003067999999999782</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.09050499999999977</v>
+        <v>-0.001534000000000387</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.440408</v>
+        <v>1.466486</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>162.6235771871129</v>
+        <v>169.1093658514498</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>34.16704910353945</v>
+        <v>53.57356867345666</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>27.96091090334701</v>
+        <v>39.40992205373428</v>
       </c>
     </row>
     <row r="20">
@@ -1263,37 +1263,37 @@
         <v>0.901</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>181.7578068293948</v>
+        <v>187.9980620635031</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>179.1210849438154</v>
+        <v>180.1757856530923</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.757828956016056</v>
+        <v>355.6054654476808</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>83.75978333770284</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.2316310000000002</v>
+        <v>0.3405440000000001</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>-0.01227200000000012</v>
+        <v>0.00613600000000006</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.1027769999999999</v>
+        <v>-0.004602000000000169</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.461884</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>160.3800437678381</v>
+        <v>168.2900399484554</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>37.82794883108549</v>
+        <v>59.63341855772402</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>28.01967712180874</v>
+        <v>39.41446306900534</v>
       </c>
     </row>
     <row r="21">
@@ -1304,37 +1304,37 @@
         <v>0.951</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>182.9882909902177</v>
+        <v>189.755839283185</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>178.593734589177</v>
+        <v>180.7031360077307</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2.548854487973699</v>
+        <v>355.1660068188154</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>82.52929917687987</v>
+        <v>83.67189161192977</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.2531070000000001</v>
+        <v>0.3712230000000002</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>-0.02147599999999996</v>
+        <v>0.0153399999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.1165830000000004</v>
+        <v>-0.01227200000000012</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.440408</v>
+        <v>1.46035</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>157.351896786239</v>
+        <v>167.4768208867178</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>40.69971866747909</v>
+        <v>65.1938386533657</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>27.61348917416296</v>
+        <v>38.99071482702399</v>
       </c>
     </row>
     <row r="22">
@@ -1345,37 +1345,37 @@
         <v>1.001</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>184.3066668768138</v>
+        <v>191.074215169781</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>177.8906007829925</v>
+        <v>181.5820532654614</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2.988255821059511</v>
+        <v>354.4628730126309</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>83.40821643461057</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.276117</v>
+        <v>0.394233</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>-0.03374800000000008</v>
+        <v>0.0306799999999998</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.1242520000000001</v>
+        <v>-0.02454400000000024</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.455748</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>155.8838238543643</v>
+        <v>167.9687898253544</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>44.17044813491893</v>
+        <v>69.87699917118078</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>28.47183909428659</v>
+        <v>38.22448714333996</v>
       </c>
     </row>
     <row r="23">
@@ -1386,37 +1386,37 @@
         <v>1.051</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>185.8007689191764</v>
+        <v>192.0410241532847</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>176.9238490952683</v>
+        <v>182.9003718562779</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>3.51560617569794</v>
+        <v>353.3203378733605</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>83.23243298306443</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.3021939999999999</v>
+        <v>0.4111069999999998</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>-0.05062100000000012</v>
+        <v>0.05368899999999991</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.1334560000000004</v>
+        <v>-0.04448500000000007</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.45268</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>153.8933122455574</v>
+        <v>169.4391045660363</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>47.97498241120518</v>
+        <v>73.86663125416823</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>29.79021613988166</v>
+        <v>37.16815374327459</v>
       </c>
     </row>
     <row r="24">
@@ -1427,37 +1427,37 @@
         <v>1.101</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>187.2949282573186</v>
+        <v>192.7441579594693</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>176.3086070148568</v>
+        <v>185.0097732748315</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>4.130848256109402</v>
+        <v>351.7382868094453</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>83.23243298306443</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.328272</v>
+        <v>0.4233789999999999</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>-0.06135899999999986</v>
+        <v>0.09050499999999977</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.1441940000000002</v>
+        <v>-0.07209700000000009</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.45268</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>151.277361560274</v>
+        <v>171.3495673030595</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>51.52435426952165</v>
+        <v>77.21552120978805</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>29.97060739305573</v>
+        <v>34.64749673002299</v>
       </c>
     </row>
     <row r="25">
@@ -1468,37 +1468,37 @@
         <v>1.151</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>188.9648710470069</v>
+        <v>193.0957248625616</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>175.7812566602184</v>
+        <v>187.4706843006979</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>4.833982062293956</v>
+        <v>350.068344019757</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>83.23243298306443</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.3574179999999999</v>
+        <v>0.429515</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>-0.0705630000000002</v>
+        <v>0.1334559999999999</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.1564660000000003</v>
+        <v>-0.1012430000000005</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.45268</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>148.09096616051</v>
+        <v>173.6243679886489</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>55.30574001227505</v>
+        <v>79.52588848400323</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>29.71012528927076</v>
+        <v>31.08565843213088</v>
       </c>
     </row>
     <row r="26">
@@ -1509,37 +1509,37 @@
         <v>1.201</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>190.6347565409156</v>
+        <v>193.3594000398808</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>175.4296897571261</v>
+        <v>190.195327799663</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>5.537115868478509</v>
+        <v>347.9589998969829</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>83.23243298306443</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.3865630000000001</v>
+        <v>0.4341170000000001</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>-0.07669900000000025</v>
+        <v>0.18101</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.1687380000000004</v>
+        <v>-0.1380579999999996</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.45268</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>144.6774442076551</v>
+        <v>176.89355322253</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>58.88991646851421</v>
+        <v>82.0102251875044</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>28.9977020063134</v>
+        <v>27.53167239231789</v>
       </c>
     </row>
     <row r="27">
@@ -1550,37 +1550,37 @@
         <v>1.251</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>192.2168076048309</v>
+        <v>193.4472917656538</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>174.9902311282607</v>
+        <v>192.8320222770756</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>6.064466223116881</v>
+        <v>345.58592330111</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>83.23243298306443</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.4141750000000001</v>
+        <v>0.4356510000000001</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>-0.08436900000000021</v>
+        <v>0.227029</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0.1779419999999998</v>
+        <v>-0.1794760000000001</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.45268</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>141.8383894303696</v>
+        <v>181.080972701933</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>62.35271374706779</v>
+        <v>84.28929264125742</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>28.90286789605278</v>
+        <v>24.63143953183871</v>
       </c>
     </row>
     <row r="28">
@@ -1591,37 +1591,37 @@
         <v>1.301</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>193.8866930987397</v>
+        <v>193.5351834914269</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>174.5507724993954</v>
+        <v>195.5566657760407</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>6.416033126209186</v>
+        <v>343.0371205494706</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>83.23243298306443</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.4433200000000003</v>
+        <v>0.4371849999999999</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>-0.09203900000000016</v>
+        <v>0.2745830000000001</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.1840780000000003</v>
+        <v>-0.2239610000000002</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.45268</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>139.3084468090294</v>
+        <v>185.5597343884484</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>66.14960142043461</v>
+        <v>86.72063098923373</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>29.19908674674949</v>
+        <v>21.60024591477676</v>
       </c>
     </row>
     <row r="29">
@@ -1632,37 +1632,37 @@
         <v>1.351</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>195.2929607111087</v>
+        <v>193.6230179214205</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>174.1992055963031</v>
+        <v>198.0175768019071</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>6.855491755074524</v>
+        <v>340.2245853247324</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>83.32032470883749</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.467864</v>
+        <v>0.4387180000000001</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>-0.09817500000000022</v>
+        <v>0.3175339999999998</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.1917480000000003</v>
+        <v>-0.2730489999999997</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.454213999999999</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>136.6903326129363</v>
+        <v>190.6360597603141</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>69.06711745904775</v>
+        <v>89.44936281468996</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>29.07176226200761</v>
+        <v>19.82381024226197</v>
       </c>
     </row>
     <row r="30">
@@ -1673,37 +1673,37 @@
         <v>1.401</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>196.7871200492509</v>
+        <v>193.7988013729666</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>173.9355304189839</v>
+        <v>200.5663795535465</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>7.294950383939863</v>
+        <v>337.3242156700006</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>83.32032470883749</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>0.4417859999999999</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>-0.1027769999999999</v>
+        <v>0.3620189999999998</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.1994180000000002</v>
+        <v>-0.3236700000000003</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.454213999999999</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>133.8380349866527</v>
+        <v>195.8368102219749</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>72.06674317532796</v>
+        <v>92.62380116518936</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>28.72514265610062</v>
+        <v>17.75630670004855</v>
       </c>
     </row>
     <row r="31">
@@ -1714,37 +1714,37 @@
         <v>1.451</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>198.0176042100739</v>
+        <v>194.326151727605</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>173.7597469674378</v>
+        <v>202.9394561494194</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>7.646459991252584</v>
+        <v>334.3359542894958</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>83.40821643461057</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.5154180000000002</v>
+        <v>0.4509900000000002</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>-0.1058450000000002</v>
+        <v>0.4034369999999999</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.2055529999999995</v>
+        <v>-0.3758250000000004</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.455748</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>131.4387239180066</v>
+        <v>200.475109088016</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>74.45919643110582</v>
+        <v>97.08541603900298</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>28.36186129535167</v>
+        <v>16.31137182465267</v>
       </c>
     </row>
     <row r="32">
@@ -1755,37 +1755,37 @@
         <v>1.501</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>199.3359228008904</v>
+        <v>194.8535020822434</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>173.4960717901186</v>
+        <v>205.2245837237397</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>8.085918620117923</v>
+        <v>331.3476356132115</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>83.49610816038363</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.5384270000000002</v>
+        <v>0.460194</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>-0.1104469999999998</v>
+        <v>0.4433200000000003</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0.2132229999999995</v>
+        <v>-0.4279809999999996</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.457282</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>128.7086120768064</v>
+        <v>205.007279773062</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>76.87680860352644</v>
+        <v>101.6201432665386</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>28.01400581677399</v>
+        <v>15.02792485729256</v>
       </c>
     </row>
     <row r="33">
@@ -1796,37 +1796,37 @@
         <v>1.551</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>200.8300821390325</v>
+        <v>195.1171772595626</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>173.2323966127994</v>
+        <v>207.4218768680664</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>8.525377248983318</v>
+        <v>328.6230494100259</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>83.75978333770284</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.5645049999999998</v>
+        <v>0.4647959999999997</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>-0.115049</v>
+        <v>0.48167</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0.2208930000000004</v>
+        <v>-0.4755340000000005</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.461884</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>125.6924814847925</v>
+        <v>208.7862003146504</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>79.59389842313483</v>
+        <v>104.6929827218692</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>27.66507875410031</v>
+        <v>13.23175947258645</v>
       </c>
     </row>
     <row r="34">
@@ -1837,37 +1837,37 @@
         <v>1.601</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>202.5000249287208</v>
+        <v>195.2050689853357</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>172.7929952797136</v>
+        <v>209.3554948350739</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>9.228511055167814</v>
+        <v>326.6015397172453</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>83.93556678924898</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.5936510000000003</v>
+        <v>0.4663300000000001</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>-0.1227180000000002</v>
+        <v>0.5154180000000002</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0.2331649999999996</v>
+        <v>-0.5108160000000004</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.464952</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>121.8104492043687</v>
+        <v>211.4431786453729</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>82.20455975040497</v>
+        <v>106.431509766519</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>27.14584001358691</v>
+        <v>10.61938213339928</v>
       </c>
     </row>
     <row r="35">
@@ -1878,37 +1878,37 @@
         <v>1.651</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>204.2578021484027</v>
+        <v>195.4687441626549</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>172.2656449250752</v>
+        <v>211.1132720547557</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>10.01953658712546</v>
+        <v>324.7558707717904</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>84.28713369234124</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.6243299999999998</v>
+        <v>0.4709320000000003</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>-0.1319220000000001</v>
+        <v>0.5460970000000002</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.2469710000000001</v>
+        <v>-0.5430290000000003</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.471088</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>117.5900105437603</v>
+        <v>212.9613451438149</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>84.71962469128717</v>
+        <v>108.4269127153248</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>26.63371071432306</v>
+        <v>8.11162466211573</v>
       </c>
     </row>
     <row r="36">
@@ -1919,37 +1919,37 @@
         <v>1.701</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>205.927744938091</v>
+        <v>195.556635888428</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>171.7382945704368</v>
+        <v>212.695323118671</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>10.98634557062923</v>
+        <v>323.3496031594213</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>84.55080886966044</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.6534760000000002</v>
+        <v>0.4724660000000002</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>-0.1411259999999999</v>
+        <v>0.5737090000000001</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0.2638450000000004</v>
+        <v>-0.5675729999999997</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.47569</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>113.0220729220476</v>
+        <v>214.0195165081066</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>86.54142743160745</v>
+        <v>109.3794026265656</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>25.73127495785951</v>
+        <v>5.174895815647972</v>
       </c>
     </row>
     <row r="37">
@@ -1960,37 +1960,37 @@
         <v>1.751</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>207.6855221577728</v>
+        <v>195.7324193399741</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>171.1230524900253</v>
+        <v>214.1894824568131</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>12.0409889841265</v>
+        <v>322.1191189985984</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>82.44140745110681</v>
+        <v>84.7265923212066</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.6841549999999997</v>
+        <v>0.475534</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>-0.1518640000000001</v>
+        <v>0.5997869999999998</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0.2822519999999998</v>
+        <v>-0.589049</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.438874</v>
+        <v>1.478758</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>108.1536447105586</v>
+        <v>214.7159878925798</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>88.20542692085652</v>
+        <v>110.5674673595275</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>24.83542251136194</v>
+        <v>2.126980025172912</v>
       </c>
     </row>
     <row r="38">
@@ -2001,37 +2001,37 @@
         <v>1.801</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>209.3554649474611</v>
+        <v>195.7324193399741</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>170.5957021353869</v>
+        <v>215.947259676495</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>13.00779796763027</v>
+        <v>321.064475585101</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>82.35351572533375</v>
+        <v>84.63870059543353</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.7133010000000002</v>
+        <v>0.475534</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>-0.161068</v>
+        <v>0.6304659999999999</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0.2991260000000001</v>
+        <v>-0.6074560000000006</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.43734</v>
+        <v>1.477224</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>103.7660954715072</v>
+        <v>215.5892875623398</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>89.78722123911349</v>
+        <v>111.0171708663738</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>23.92907273050895</v>
+        <v>-2.396786838367717</v>
       </c>
     </row>
     <row r="39">
@@ -2042,37 +2042,37 @@
         <v>1.851</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>210.9375160113764</v>
+        <v>195.9082027915202</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>170.1562435065215</v>
+        <v>217.5293107404102</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>13.88671522536094</v>
+        <v>319.8339914242781</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>82.26562399956067</v>
+        <v>84.7265923212066</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.7409130000000002</v>
+        <v>0.4786020000000002</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>-0.1687379999999999</v>
+        <v>0.6580779999999999</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0.314466</v>
+        <v>-0.6289319999999999</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.435806</v>
+        <v>1.478758</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>99.66137174372417</v>
+        <v>216.2594112155551</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>91.1667475166399</v>
+        <v>112.2030008198249</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>23.01577160903366</v>
+        <v>-5.894672943339884</v>
       </c>
     </row>
     <row r="40">
@@ -2083,37 +2083,37 @@
         <v>1.901</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>212.343726327966</v>
+        <v>195.9082027915202</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>169.8046766034292</v>
+        <v>219.0234127827728</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>14.67774075731859</v>
+        <v>318.6035072634552</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>82.00194882224147</v>
+        <v>84.7265923212066</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.7654560000000002</v>
+        <v>0.4786020000000002</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>-0.174874</v>
+        <v>0.6841549999999997</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0.3282720000000005</v>
+        <v>-0.6504079999999994</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.431204000000001</v>
+        <v>1.478758</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>96.34920376077331</v>
+        <v>217.5427523098661</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>92.58102669902003</v>
+        <v>112.8688433884684</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>22.09237081291798</v>
+        <v>-9.076808303275243</v>
       </c>
     </row>
     <row r="41">
@@ -2124,37 +2124,37 @@
         <v>1.951</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>213.662102214562</v>
+        <v>195.9960945172933</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>169.54100142611</v>
+        <v>220.2538969435958</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>15.46876628927618</v>
+        <v>317.4609148284053</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>81.6503819191492</v>
+        <v>84.81448404697966</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.788466</v>
+        <v>0.4801360000000001</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>-0.1794760000000001</v>
+        <v>0.7056310000000002</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0.342078</v>
+        <v>-0.6703499999999996</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.425068</v>
+        <v>1.480292</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>93.28621770060828</v>
+        <v>218.4933985355109</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>93.86035460636121</v>
+        <v>113.7878042906427</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>20.97799088297856</v>
+        <v>-11.45176382393606</v>
       </c>
     </row>
     <row r="42">
@@ -2165,37 +2165,37 @@
         <v>2.001</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>214.980478101158</v>
+        <v>195.9960945172933</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>169.3652179745639</v>
+        <v>221.3964893786457</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>16.34768354700685</v>
+        <v>316.4941631406811</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>81.38670674183</v>
+        <v>85.16599365429242</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.8114759999999999</v>
+        <v>0.4801360000000001</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>-0.1825439999999999</v>
+        <v>0.7255730000000004</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.3574179999999999</v>
+        <v>-0.6872229999999996</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.420466</v>
+        <v>1.486427</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>89.77625113922259</v>
+        <v>218.5601367556582</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>94.5850861055944</v>
+        <v>113.8225604690157</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>19.50593496427362</v>
+        <v>-13.94507555386866</v>
       </c>
     </row>
     <row r="43">
@@ -2206,37 +2206,37 @@
         <v>2.051</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>216.1230705362079</v>
+        <v>195.9960945172933</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>169.1015427972447</v>
+        <v>222.4511900879225</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>17.226543508958</v>
+        <v>315.7031376087234</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>80.77146466141852</v>
+        <v>85.5175605573847</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.831418</v>
+        <v>0.4801360000000001</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>-0.1871460000000001</v>
+        <v>0.743981</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0.3727569999999996</v>
+        <v>-0.701029</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.409728</v>
+        <v>1.492563</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>87.30775639583932</v>
+        <v>218.250655196058</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>95.73741705919836</v>
+        <v>113.6613875119773</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>18.19641877162164</v>
+        <v>-16.49499767645443</v>
       </c>
     </row>
     <row r="44">
@@ -2247,37 +2247,37 @@
         <v>2.101</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>217.2656056754782</v>
+        <v>195.9960945172933</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>169.0136510714716</v>
+        <v>223.2422156198801</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>18.19335249246177</v>
+        <v>315.0000038025389</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>80.06838815101348</v>
+        <v>85.60545228315776</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.8513589999999998</v>
+        <v>0.4801360000000001</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>-0.18868</v>
+        <v>0.757787</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.3896309999999998</v>
+        <v>-0.7133010000000002</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.397457</v>
+        <v>1.494097</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>84.67403226335459</v>
+        <v>218.7380074122801</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>96.65181284884011</v>
+        <v>113.9151926107664</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>16.34244379055585</v>
+        <v>-18.15012691204808</v>
       </c>
     </row>
     <row r="45">
@@ -2288,37 +2288,37 @@
         <v>2.151</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>218.1445229332089</v>
+        <v>195.9960945172933</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>168.8378676199255</v>
+        <v>223.9452921302851</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>19.07226975019245</v>
+        <v>314.3847617221274</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>79.27736261905586</v>
+        <v>85.86912746047696</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.8666989999999997</v>
+        <v>0.4801360000000001</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>-0.1917479999999998</v>
+        <v>0.7700579999999999</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0.4049709999999997</v>
+        <v>-0.7240389999999999</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.383651</v>
+        <v>1.498699</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>82.88479056023687</v>
+        <v>218.6544326264918</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>97.58995191451267</v>
+        <v>113.8716682231527</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>14.84447149386182</v>
+        <v>-19.66884832925848</v>
       </c>
     </row>
     <row r="46">
@@ -2329,37 +2329,37 @@
         <v>2.201</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>218.8476567393935</v>
+        <v>196.0839862430664</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>168.5741924426063</v>
+        <v>224.3847507591505</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>19.86329528215009</v>
+        <v>313.9453030932621</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>78.57422881287131</v>
+        <v>86.22069436356924</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.8789709999999998</v>
+        <v>0.48167</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>-0.1963499999999999</v>
+        <v>0.7777279999999999</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0.4187770000000003</v>
+        <v>-0.7317089999999998</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.371379</v>
+        <v>1.504835</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>81.46550640805174</v>
+        <v>218.0869228417931</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>98.33966439117188</v>
+        <v>114.0017380031763</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>13.71245788839542</v>
+        <v>-20.51006915634562</v>
       </c>
     </row>
     <row r="47">
@@ -2370,37 +2370,37 @@
         <v>2.251</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>219.3750070940319</v>
+        <v>195.9960945172933</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>168.3105745610666</v>
+        <v>224.6484259364697</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>20.74221253988077</v>
+        <v>313.6816279159428</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>77.95898673245985</v>
+        <v>86.74804471820764</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.8881750000000002</v>
+        <v>0.4801360000000001</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>-0.2009509999999999</v>
+        <v>0.78233</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.4341170000000001</v>
+        <v>-0.736311</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.360641</v>
+        <v>1.514039</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>79.98918716466163</v>
+        <v>217.2115587004246</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>98.38694656890945</v>
+        <v>113.1202429763678</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>12.40726238987085</v>
+        <v>-21.02626312813396</v>
       </c>
     </row>
     <row r="48">
@@ -2411,37 +2411,37 @@
         <v>2.301</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>219.9023574486703</v>
+        <v>196.0839862430664</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>168.2226828352935</v>
+        <v>224.6484259364697</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>21.44528905028579</v>
+        <v>313.2421692870775</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>77.43163637782143</v>
+        <v>87.09961162129993</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.897379</v>
+        <v>0.48167</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>-0.2024849999999997</v>
+        <v>0.78233</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0.4463880000000001</v>
+        <v>-0.743981</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.351437</v>
+        <v>1.520175</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>78.60111812225061</v>
+        <v>217.2985701586088</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>98.51843611397564</v>
+        <v>113.5896382088769</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>11.11634757984231</v>
+        <v>-20.07310714759791</v>
       </c>
     </row>
     <row r="49">
@@ -2452,37 +2452,37 @@
         <v>2.351</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>220.4297078033087</v>
+        <v>196.0839862430664</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>168.1347911095204</v>
+        <v>224.6484259364697</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>21.97263940492422</v>
+        <v>312.9784941097583</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>76.9921777489561</v>
+        <v>87.36328679861913</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.9065829999999998</v>
+        <v>0.48167</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>-0.2040190000000001</v>
+        <v>0.78233</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0.4555920000000004</v>
+        <v>-0.7485830000000001</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.343767000000001</v>
+        <v>1.524777</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>77.42414601969492</v>
+        <v>217.3167964289642</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>98.89678652384147</v>
+        <v>113.599165724194</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>10.19073015449931</v>
+        <v>-19.50283037732274</v>
       </c>
     </row>
     <row r="50">
@@ -2493,37 +2493,37 @@
         <v>2.401</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>221.0448925879407</v>
+        <v>196.0839862430664</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>168.1347911095204</v>
+        <v>224.6484259364697</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>22.41209803378956</v>
+        <v>312.8027106582122</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>76.64061084586382</v>
+        <v>87.62696197593833</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.9173200000000004</v>
+        <v>0.48167</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>-0.2040190000000001</v>
+        <v>0.78233</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0.4632620000000003</v>
+        <v>-0.751651</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.337631</v>
+        <v>1.529379</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>76.05728869526756</v>
+        <v>217.1024066005816</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>99.32984542244751</v>
+        <v>113.4870965880563</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>9.276938036531277</v>
+        <v>-19.12552029509749</v>
       </c>
     </row>
     <row r="51">
@@ -2534,37 +2534,37 @@
         <v>2.451</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>221.6601346683522</v>
+        <v>195.9960945172933</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>168.1347911095204</v>
+        <v>224.6484259364697</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>22.58788148533569</v>
+        <v>312.8027106582122</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>87.71485370171139</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.928058</v>
+        <v>0.4801360000000001</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>-0.2040190000000001</v>
+        <v>0.78233</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0.4663300000000001</v>
+        <v>-0.751651</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.530913</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>74.92752799099726</v>
+        <v>217.050807755531</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>100.0622916747628</v>
+        <v>113.0365265017297</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>8.909368611395678</v>
+        <v>-19.12805480258436</v>
       </c>
     </row>
     <row r="52">
@@ -2575,37 +2575,37 @@
         <v>2.501</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>222.1874850229906</v>
+        <v>195.9960945172933</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>168.1347911095204</v>
+        <v>224.6484259364697</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>22.67577321110878</v>
+        <v>312.8027106582122</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>76.55271912009076</v>
+        <v>87.80274542748447</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.9372619999999999</v>
+        <v>0.4801360000000001</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>-0.2040190000000001</v>
+        <v>0.78233</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.4678640000000005</v>
+        <v>-0.751651</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.336097</v>
+        <v>1.532447</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>73.67327282334867</v>
+        <v>216.8253720273622</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>100.2982520823777</v>
+        <v>112.9191232452061</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>8.739732271602151</v>
+        <v>-19.13019940871524</v>
       </c>
     </row>
     <row r="53">
@@ -2616,37 +2616,37 @@
         <v>2.551</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>222.802727103402</v>
+        <v>195.8203110657471</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>168.1347911095204</v>
+        <v>224.6484259364697</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>22.8515566626549</v>
+        <v>312.8027106582122</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>88.15431233057674</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.9480000000000002</v>
+        <v>0.4770679999999998</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>-0.2040190000000001</v>
+        <v>0.78233</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.4709320000000003</v>
+        <v>-0.751651</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.538583000000001</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>72.3856409536365</v>
+        <v>216.2675862127014</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>100.796145024649</v>
+        <v>111.786517355693</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>8.380220317090533</v>
+        <v>-19.13487873250955</v>
       </c>
     </row>
     <row r="54">
@@ -2657,37 +2657,37 @@
         <v>2.601</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>223.3300774580404</v>
+        <v>195.9082027915202</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>168.1347911095204</v>
+        <v>224.4726424849235</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>23.20312356574715</v>
+        <v>312.8027106582122</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>88.76955441098822</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.9572039999999999</v>
+        <v>0.4786020000000002</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>-0.2040190000000001</v>
+        <v>0.7792619999999997</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0.4770679999999998</v>
+        <v>-0.751651</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.549321</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>70.75290016756308</v>
+        <v>214.775967175565</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>100.4613968596693</v>
+        <v>111.433337793834</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7.681224913045611</v>
+        <v>-18.42297708619125</v>
       </c>
     </row>
     <row r="55">
@@ -2698,37 +2698,37 @@
         <v>2.651</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>223.5937526353597</v>
+        <v>195.8203110657471</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>168.1347911095204</v>
+        <v>224.4726424849235</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>23.46679874306636</v>
+        <v>312.8027106582122</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>89.91208955025859</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.9618060000000002</v>
+        <v>0.4770679999999998</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>-0.2040190000000001</v>
+        <v>0.7792619999999997</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0.48167</v>
+        <v>-0.751651</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.569262</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>69.76520188778657</v>
+        <v>212.0117917359228</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>100.0336933731107</v>
+        <v>109.5867404428792</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>7.161894493652426</v>
+        <v>-18.36976186953316</v>
       </c>
     </row>
     <row r="56">
@@ -2739,37 +2739,37 @@
         <v>2.701</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>224.033211264225</v>
+        <v>195.8203110657471</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>168.1347911095204</v>
+        <v>224.3847507591505</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>23.73047392038558</v>
+        <v>312.8027106582122</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>91.40624888840075</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.9694760000000001</v>
+        <v>0.4770679999999998</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>-0.2040190000000001</v>
+        <v>0.7777279999999999</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0.4862720000000002</v>
+        <v>-0.751651</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.59534</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>68.4757100448313</v>
+        <v>208.3050053930814</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>99.80763697863107</v>
+        <v>107.6707402548512</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>6.646790131995857</v>
+        <v>-17.85960277614629</v>
       </c>
     </row>
     <row r="57">
@@ -2780,37 +2780,37 @@
         <v>2.751</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>224.2089947157711</v>
+        <v>195.7324193399741</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>168.1347911095204</v>
+        <v>224.2089673076044</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>23.73047392038558</v>
+        <v>312.8027106582122</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>92.98829995231598</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.9725439999999999</v>
+        <v>0.475534</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>-0.2040190000000001</v>
+        <v>0.77466</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0.4862720000000002</v>
+        <v>-0.751651</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.622952</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>68.16917842715054</v>
+        <v>204.6664843608119</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>100.0172504019648</v>
+        <v>105.3925003501583</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>6.646790131995857</v>
+        <v>-16.89602106820868</v>
       </c>
     </row>
     <row r="58">
@@ -2821,37 +2821,37 @@
         <v>2.801</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>224.5605616188634</v>
+        <v>195.7324193399741</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>168.2226828352935</v>
+        <v>223.5937252271929</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>23.81836564615861</v>
+        <v>312.626927206666</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>94.65818544622476</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.9786799999999999</v>
+        <v>0.475534</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>-0.2024849999999997</v>
+        <v>0.7639219999999998</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0.4878059999999996</v>
+        <v>-0.7547189999999997</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.652097</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>67.32281436512936</v>
+        <v>201.7206164436644</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>100.0896573496215</v>
+        <v>103.8755329460467</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>6.309316991594415</v>
+        <v>-13.83276927697477</v>
       </c>
     </row>
     <row r="59">
@@ -2862,37 +2862,37 @@
         <v>2.851</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>224.9121285219557</v>
+        <v>195.7324193399741</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>168.3105745610666</v>
+        <v>222.2754066363764</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>23.81836564615861</v>
+        <v>312.4511437551199</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>96.50391168745919</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.984816</v>
+        <v>0.475534</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>-0.2009509999999999</v>
+        <v>0.7409130000000002</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0.4878059999999996</v>
+        <v>-0.7577869999999995</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.684311</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>66.6477853961477</v>
+        <v>199.2335023661959</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>100.4110473503459</v>
+        <v>102.594799698006</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>6.142769462630696</v>
+        <v>-8.088502701580182</v>
       </c>
     </row>
     <row r="60">
@@ -2903,37 +2903,37 @@
         <v>2.901</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>225.1758036992749</v>
+        <v>195.7324193399741</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>168.3105745610666</v>
+        <v>220.6933555724611</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>23.99414909770479</v>
+        <v>312.3633093251264</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>98.34963792869364</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.9894180000000001</v>
+        <v>0.475534</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>-0.2009509999999999</v>
+        <v>0.7133010000000002</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0.4908740000000004</v>
+        <v>-0.7593199999999997</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.716525</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>65.84676619804225</v>
+        <v>196.7266997685121</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>100.2020061735797</v>
+        <v>101.3039278951347</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>5.804550416426309</v>
+        <v>-1.582275714119561</v>
       </c>
     </row>
     <row r="61">
@@ -2944,37 +2944,37 @@
         <v>2.951</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>225.351587150821</v>
+        <v>195.644527614201</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>168.3105745610666</v>
+        <v>219.1113045085459</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>312.3633093251264</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>100.2831985999216</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.992486</v>
+        <v>0.4740000000000001</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>-0.2009509999999999</v>
+        <v>0.6856890000000002</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.7593199999999997</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.750272000000001</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>65.20182863683593</v>
+        <v>193.7734960936814</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>99.88696048505453</v>
+        <v>99.4074092769539</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>5.468222460551601</v>
+        <v>4.722169797978523</v>
       </c>
     </row>
     <row r="62">
@@ -2985,37 +2985,37 @@
         <v>3.001</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>225.4394788765941</v>
+        <v>195.556635888428</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>168.3105745610666</v>
+        <v>217.7050941919563</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>312.3633093251264</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>101.8652496638368</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.9940199999999998</v>
+        <v>0.4724660000000002</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>-0.2009509999999999</v>
+        <v>0.6611460000000001</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.7593199999999997</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.777884</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>65.04852538452413</v>
+        <v>191.3835323842497</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>99.98686252617935</v>
+        <v>97.81078280287724</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>5.468222460551601</v>
+        <v>10.22832114946505</v>
       </c>
     </row>
     <row r="63">
@@ -3026,37 +3026,37 @@
         <v>3.051</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>225.4394788765941</v>
+        <v>195.2929607111087</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>168.3105745610666</v>
+        <v>216.2109348538142</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>312.3633093251264</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>103.359409001979</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.9940199999999998</v>
+        <v>0.467864</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>-0.2009509999999999</v>
+        <v>0.6350680000000001</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.7593199999999997</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.803962</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>65.04852538452413</v>
+        <v>189.4734489175251</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>99.98686252617935</v>
+        <v>95.73745781140269</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>5.468222460551601</v>
+        <v>15.95588519171284</v>
       </c>
     </row>
     <row r="64">
@@ -3067,37 +3067,37 @@
         <v>3.101</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>225.4394788765941</v>
+        <v>194.8535020822434</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>214.6288837898989</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>312.3633093251264</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>104.6777275927955</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.9940199999999998</v>
+        <v>0.460194</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.607456</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.7593199999999997</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.826971</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>64.98907533007211</v>
+        <v>188.2302284179286</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>99.89548113995224</v>
+        <v>93.30391974420323</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>21.86190735460352</v>
       </c>
     </row>
     <row r="65">
@@ -3108,37 +3108,37 @@
         <v>3.151</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>225.4394788765941</v>
+        <v>194.2382600018319</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>213.2226734733094</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>312.4511437551199</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>105.8203200278454</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.9940199999999998</v>
+        <v>0.4494559999999998</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.582913</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.7577869999999995</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.846913</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>64.98907533007211</v>
+        <v>187.2133000905457</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>99.89548113995224</v>
+        <v>90.30875740001197</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>26.87394687003007</v>
       </c>
     </row>
     <row r="66">
@@ -3149,37 +3149,37 @@
         <v>3.201</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>225.5273706023672</v>
+        <v>193.4472917656538</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>211.5527306836211</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>312.626927206666</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>106.3476703824838</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.9955540000000003</v>
+        <v>0.4356510000000001</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.5537670000000001</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.7547189999999997</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.856117</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>64.83575925740156</v>
+        <v>187.9093109533333</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>99.99505680760728</v>
+        <v>87.46773702742252</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>32.38892195119979</v>
       </c>
     </row>
     <row r="67">
@@ -3190,37 +3190,37 @@
         <v>3.251</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>225.5273706023672</v>
+        <v>192.6562662336962</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>209.6191127166136</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>312.626927206666</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>106.4355621082569</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.9955540000000003</v>
+        <v>0.421845</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.520019</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.7547189999999997</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.857651</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>64.83575925740156</v>
+        <v>190.1238081867877</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>99.99505680760728</v>
+        <v>85.32515367744507</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>39.01578893487877</v>
       </c>
     </row>
     <row r="68">
@@ -3231,37 +3231,37 @@
         <v>3.301</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>225.5273706023672</v>
+        <v>191.7773489759655</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>207.3339851422933</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>313.0663858355314</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>106.4355621082569</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.9955540000000003</v>
+        <v>0.4065050000000002</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.4801360000000001</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.7470489999999997</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.857651</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>64.83575925740156</v>
+        <v>191.7060608124683</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>99.99505680760728</v>
+        <v>82.5260601576925</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>45.98028225481917</v>
       </c>
     </row>
     <row r="69">
@@ -3272,37 +3272,37 @@
         <v>3.351</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>191.3378903471002</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>205.664042352605</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>313.9453030932621</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>106.3476703824838</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.3988350000000002</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.4509900000000002</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.7317089999999998</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.856117</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>191.4664381905013</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>80.68791000262928</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>49.89702126732959</v>
       </c>
     </row>
     <row r="70">
@@ -3313,37 +3313,37 @@
         <v>3.401</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>190.9863234440079</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>204.3457237617885</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>315.3515707056312</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>105.9082117536185</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.3926990000000001</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.4279810000000001</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.7071649999999996</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.848447</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>190.7004302196196</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>78.99068629426701</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>51.46531782928764</v>
       </c>
     </row>
     <row r="71">
@@ -3354,37 +3354,37 @@
         <v>3.451</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>190.7226482666887</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>203.5546982298309</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>317.3730231026322</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>105.0292944958878</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.388097</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.4141750000000001</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.6718839999999999</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.833107</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>189.4072243771215</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>77.43575493771411</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>49.92411374162046</v>
       </c>
     </row>
     <row r="72">
@@ -3395,37 +3395,37 @@
         <v>3.501</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>190.5468648151426</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>202.5878892463271</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>320.1855583273704</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>103.7109186092918</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.3850290000000002</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.3973009999999998</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.6227960000000005</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.810097</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>187.4251776649096</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>75.95513775820633</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>47.28437624446437</v>
       </c>
     </row>
     <row r="73">
@@ -3436,37 +3436,37 @@
         <v>3.551</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>190.2831896378234</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>201.5331885370503</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>323.7011700625136</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>101.7773579380638</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.380427</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.3788930000000001</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.5614370000000001</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.77635</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>185.4889547640792</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>74.1785030978409</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>43.39796231814975</v>
       </c>
     </row>
     <row r="74">
@@ -3477,37 +3477,37 @@
         <v>3.601</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>189.6679475574119</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>199.7754113173685</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>327.3046735234299</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>99.31638961641787</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.3696889999999998</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.3482140000000001</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.4985440000000003</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.733397999999999</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>185.3726009896431</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>71.83288734928703</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>41.51190009445551</v>
       </c>
     </row>
     <row r="75">
@@ -3518,37 +3518,37 @@
         <v>3.651</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>188.7890875954607</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>197.4902264472687</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>330.9960687101192</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>96.24023651013999</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.3543500000000001</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.3083299999999999</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.4341170000000001</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.679709</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>187.1320786746398</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>69.23250387279697</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>41.06058783200959</v>
       </c>
     </row>
     <row r="76">
@@ -3559,37 +3559,37 @@
         <v>3.701</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>187.7343868861839</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>195.8203409533599</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>335.0390880956804</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>93.16408340386212</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.335942</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.2791850000000002</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.3635530000000002</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.626020000000001</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>187.622410964179</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>65.51354711060766</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>37.74974217910201</v>
       </c>
     </row>
     <row r="77">
@@ -3600,37 +3600,37 @@
         <v>3.751</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>186.5039027253609</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>194.2382898894447</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>338.9062667339159</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>89.91208955025859</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.314466</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.2515730000000002</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.2960580000000003</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.569262</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>188.8679520595284</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>61.43097242099655</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>34.48630505162379</v>
       </c>
     </row>
     <row r="78">
@@ -3641,37 +3641,37 @@
         <v>3.801</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>184.4824503283599</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>193.0956974543948</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>342.7734453721513</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>87.01171989552685</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.2791850000000002</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.2316310000000002</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.2285630000000004</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.518641000000001</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>189.2504473403097</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>54.25283111120314</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>29.69113296401139</v>
       </c>
     </row>
     <row r="79">
@@ -3682,37 +3682,37 @@
         <v>3.851</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>182.1093737324871</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>192.4804553739833</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>346.0253819299754</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>84.37502541811432</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.2377670000000002</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.220893</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.1718060000000002</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.472622</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>189.9444005433272</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>46.03326581838706</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>24.54670341924137</v>
       </c>
     </row>
     <row r="80">
@@ -3723,37 +3723,37 @@
         <v>3.901</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>179.9999723139334</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>192.3925636482102</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>348.7500254289405</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>82.52929917687987</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.2009509999999999</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.2193590000000001</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.1242520000000001</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.440408</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>188.6878202127272</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>38.4357664498462</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>18.83787813015198</v>
       </c>
     </row>
     <row r="81">
@@ -3764,37 +3764,37 @@
         <v>3.951</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>225.5273706023672</v>
+        <v>178.2421950942515</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>192.4804553739833</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>350.9472612774877</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>81.29881501605693</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.9955540000000003</v>
+        <v>0.1702719999999998</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.220893</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.0859029999999996</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.418932000000001</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>64.83575925740156</v>
+        <v>186.3945988654881</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>99.99505680760728</v>
+        <v>32.04810018991633</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>13.7670754386684</v>
       </c>
     </row>
     <row r="82">
@@ -3805,37 +3805,37 @@
         <v>4.001</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>176.8359274818825</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>192.3925636482102</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>352.2656371640837</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.85935638719158</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.1457280000000001</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.2193590000000001</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.06289299999999975</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.411262</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>184.2974647765241</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>27.04904965178875</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>11.18832011835443</v>
       </c>
     </row>
     <row r="83">
@@ -3846,37 +3846,37 @@
         <v>4.051</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>175.4296598695134</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>192.4804553739833</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>352.9687709702683</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.85935638719158</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.1211839999999998</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.220893</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.05062099999999963</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.411262</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>182.5407762383782</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>22.22994787370262</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>9.429154900854542</v>
       </c>
     </row>
     <row r="84">
@@ -3887,37 +3887,37 @@
         <v>4.101</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>174.3750164560161</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>192.3046719224372</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>353.3203378733605</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.77146466141852</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.1027769999999999</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.2178250000000002</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.04448500000000007</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.409728</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>182.2361618339909</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>18.7959137693775</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>9.214569627212882</v>
       </c>
     </row>
     <row r="85">
@@ -3928,37 +3928,37 @@
         <v>4.151</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.9355578271507</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>168.4863007168332</v>
+        <v>192.040996745118</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>353.3203378733605</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.77146466141852</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.09510699999999994</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>-0.1978839999999998</v>
+        <v>0.213223</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.04448500000000007</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.409728</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>64.6229457652239</v>
+        <v>182.6814071068389</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>100.0025623427098</v>
+        <v>17.42685625329595</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>5.139516890702566</v>
+        <v>10.00315512100411</v>
       </c>
     </row>
     <row r="86">
@@ -3969,37 +3969,37 @@
         <v>4.201</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.6718826498315</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>191.9531050193449</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>353.4082295991336</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.77146466141852</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.09050499999999977</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.2116890000000001</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.04295099999999968</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.409728</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>182.5762504228843</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>16.56932891595871</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>10.08054638249217</v>
       </c>
     </row>
     <row r="87">
@@ -4010,37 +4010,37 @@
         <v>4.251</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.5839909240584</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>191.8652132935718</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>353.4961213249067</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.85935638719158</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.08897099999999988</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.2101550000000002</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.04141700000000029</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.411262</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>182.1647198606868</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>16.250278129855</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>10.15979946992204</v>
       </c>
     </row>
     <row r="88">
@@ -4051,37 +4051,37 @@
         <v>4.301</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.4960991982854</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>168.4863007168332</v>
+        <v>191.8652132935718</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>353.6718474806733</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.77146466141852</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.08743699999999999</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>-0.1978839999999998</v>
+        <v>0.2101550000000002</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.03834999999999975</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.409728</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>64.6229457652239</v>
+        <v>181.8722013890816</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>100.0025623427098</v>
+        <v>15.94300971588775</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>5.139516890702566</v>
+        <v>9.787523890041911</v>
       </c>
     </row>
     <row r="89">
@@ -4092,37 +4092,37 @@
         <v>4.351</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.4082074725123</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>168.4863007168332</v>
+        <v>191.9531050193449</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>353.7597392064463</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.77146466141852</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.0859030000000001</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>-0.1978839999999998</v>
+        <v>0.2116890000000001</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.03681600000000036</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.409728</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>64.6229457652239</v>
+        <v>181.5082303243119</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>100.0025623427098</v>
+        <v>15.63056812021191</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>5.139516890702566</v>
+        <v>9.34192225495525</v>
       </c>
     </row>
     <row r="90">
@@ -4133,37 +4133,37 @@
         <v>4.401</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.3203157467393</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>168.4863007168332</v>
+        <v>191.9531050193449</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>353.6718474806733</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.85935638719158</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.08436900000000021</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>-0.1978839999999998</v>
+        <v>0.2116890000000001</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.03834999999999975</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.411262</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>64.6229457652239</v>
+        <v>181.56482752507</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>100.0025623427098</v>
+        <v>15.35489293263024</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>5.139516890702566</v>
+        <v>9.529262512683687</v>
       </c>
     </row>
     <row r="91">
@@ -4174,37 +4174,37 @@
         <v>4.451</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.2324240209662</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>168.4863007168332</v>
+        <v>191.9531050193449</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>353.6718474806733</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.77146466141852</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.08283499999999983</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>-0.1978839999999998</v>
+        <v>0.2116890000000001</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.03834999999999975</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.409728</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>64.6229457652239</v>
+        <v>181.8414589828169</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>100.0025623427098</v>
+        <v>15.09738398506673</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>5.139516890702566</v>
+        <v>9.52594864157453</v>
       </c>
     </row>
     <row r="92">
@@ -4215,37 +4215,37 @@
         <v>4.501</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.3203157467393</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>168.4863007168332</v>
+        <v>191.8652132935718</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>353.7597392064463</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>76.37693566854462</v>
+        <v>80.77146466141852</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.08436900000000021</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>-0.1978839999999998</v>
+        <v>0.2101550000000002</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.03681600000000036</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.333029</v>
+        <v>1.409728</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>64.76066358825818</v>
+        <v>181.6344485419715</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>100.2156775917998</v>
+        <v>15.36078076495413</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5.124514113066567</v>
+        <v>9.603057288999565</v>
       </c>
     </row>
     <row r="93">
@@ -4256,37 +4256,37 @@
         <v>4.551</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.4082074725123</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>168.4863007168332</v>
+        <v>191.8652132935718</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>353.8476309322194</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.85935638719158</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.0859030000000001</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>-0.1978839999999998</v>
+        <v>0.2101550000000002</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.03528199999999997</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.411262</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>64.6229457652239</v>
+        <v>181.0713976379667</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>100.0025623427098</v>
+        <v>15.59295030503706</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>5.139516890702566</v>
+        <v>9.422734654209506</v>
       </c>
     </row>
     <row r="94">
@@ -4297,37 +4297,37 @@
         <v>4.601</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.4082074725123</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>168.4863007168332</v>
+        <v>191.8652132935718</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>354.0234143837656</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.85935638719158</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.0859030000000001</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>-0.1978839999999998</v>
+        <v>0.2101550000000002</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.03221400000000019</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.411262</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>64.6229457652239</v>
+        <v>180.4984597578232</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>100.0025623427098</v>
+        <v>15.54361180094702</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>5.139516890702566</v>
+        <v>9.056783989750471</v>
       </c>
     </row>
     <row r="95">
@@ -4338,37 +4338,37 @@
         <v>4.651</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.4082074725123</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>191.8652132935718</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>354.0234143837656</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.85935638719158</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.0859030000000001</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.2101550000000002</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.03221400000000019</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.411262</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>180.4984597578232</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>15.54361180094702</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>9.056783989750471</v>
       </c>
     </row>
     <row r="96">
@@ -4379,37 +4379,37 @@
         <v>4.701</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.4082074725123</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>168.3105745610666</v>
+        <v>191.8652132935718</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>354.0234143837656</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>76.37693566854462</v>
+        <v>80.77146466141852</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.0859030000000001</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>-0.2009509999999999</v>
+        <v>0.2101550000000002</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.03221400000000019</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.333029</v>
+        <v>1.409728</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>64.87920218224343</v>
+        <v>180.7516668582662</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>100.3991134131579</v>
+        <v>15.56541671207928</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>5.453997974774637</v>
+        <v>9.052300503544672</v>
       </c>
     </row>
     <row r="97">
@@ -4420,37 +4420,37 @@
         <v>4.751</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.4960991982854</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>191.8652132935718</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>354.0234143837656</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.77146466141852</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.08743699999999999</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.2101550000000002</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.03221400000000019</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.409728</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>180.7275768500014</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>15.84267134637212</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>9.052300503544672</v>
       </c>
     </row>
     <row r="98">
@@ -4461,37 +4461,37 @@
         <v>4.801</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.5839909240584</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>191.8652132935718</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>354.0234143837656</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.77146466141852</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.08897099999999988</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.2101550000000002</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.03221400000000019</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.409728</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>180.7030615616382</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>16.11988870039514</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>9.052300503544672</v>
       </c>
     </row>
     <row r="99">
@@ -4502,37 +4502,37 @@
         <v>4.851</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.5839909240584</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>191.9531050193449</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>354.0234143837656</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.85935638719158</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.08897099999999988</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.2116890000000001</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.03221400000000019</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.411262</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>180.3466756549677</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>16.08809675896221</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>8.797362044904474</v>
       </c>
     </row>
     <row r="100">
@@ -4543,37 +4543,37 @@
         <v>4.901</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.5839909240584</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>168.3984089910601</v>
+        <v>191.8652132935718</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>354.0234143837656</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.77146466141852</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.08897099999999988</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>-0.1994180000000002</v>
+        <v>0.2101550000000002</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.03221400000000019</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.409728</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>180.7030615616382</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>16.11988870039514</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>9.052300503544672</v>
       </c>
     </row>
     <row r="101">
@@ -4581,126 +4581,44 @@
         <v>99</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>4.951</v>
+        <v>4.917</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>225.6152623281402</v>
+        <v>173.5839909240584</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>168.4863007168332</v>
+        <v>191.8652132935718</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>24.16993254925092</v>
+        <v>354.0234143837656</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>76.46482739431768</v>
+        <v>80.77146466141852</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.9970880000000001</v>
+        <v>0.08897099999999988</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>-0.1978839999999998</v>
+        <v>0.2101550000000002</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>0.4939420000000002</v>
+        <v>-0.03221400000000019</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.334563</v>
+        <v>1.409728</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>64.6229457652239</v>
+        <v>180.7030615616382</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>100.0025623427098</v>
+        <v>16.11988870039514</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>5.139516890702566</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>100</v>
-      </c>
-      <c r="B102" s="2" t="n">
-        <v>5.001</v>
-      </c>
-      <c r="C102" s="2" t="n">
-        <v>225.6152623281402</v>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>168.4863007168332</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>24.16993254925092</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>76.46482739431768</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>0.9970880000000001</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>-0.1978839999999998</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>0.4939420000000002</v>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>1.334563</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>64.6229457652239</v>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>100.0025623427098</v>
-      </c>
-      <c r="M102" s="2" t="n">
-        <v>5.139516890702566</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>101</v>
-      </c>
-      <c r="B103" s="2" t="n">
-        <v>5.016</v>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v>225.6152623281402</v>
-      </c>
-      <c r="D103" s="2" t="n">
-        <v>168.4863007168332</v>
-      </c>
-      <c r="E103" s="2" t="n">
-        <v>24.16993254925092</v>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>76.46482739431768</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>0.9970880000000001</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>-0.1978839999999998</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>0.4939420000000002</v>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>1.334563</v>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>64.6229457652239</v>
-      </c>
-      <c r="L103" s="2" t="n">
-        <v>100.0025623427098</v>
-      </c>
-      <c r="M103" s="2" t="n">
-        <v>5.139516890702566</v>
+        <v>9.052300503544672</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M103"/>
+  <autoFilter ref="A1:M101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
